--- a/artfynd/A 24811-2026 artfynd.xlsx
+++ b/artfynd/A 24811-2026 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134285052</v>
+        <v>134285060</v>
       </c>
       <c r="B6" t="n">
-        <v>91956</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505380</v>
+        <v>505319</v>
       </c>
       <c r="R6" t="n">
-        <v>7115115</v>
+        <v>7114993</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134285060</v>
+        <v>134285052</v>
       </c>
       <c r="B7" t="n">
-        <v>91974</v>
+        <v>91956</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505319</v>
+        <v>505380</v>
       </c>
       <c r="R7" t="n">
-        <v>7114993</v>
+        <v>7115115</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285071</v>
+        <v>134285054</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>91956</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505440</v>
+        <v>505637</v>
       </c>
       <c r="R8" t="n">
-        <v>7115147</v>
+        <v>7115293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285054</v>
+        <v>134285071</v>
       </c>
       <c r="B9" t="n">
-        <v>91956</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505637</v>
+        <v>505440</v>
       </c>
       <c r="R9" t="n">
-        <v>7115293</v>
+        <v>7115147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285017</v>
+        <v>134285077</v>
       </c>
       <c r="B16" t="n">
-        <v>91960</v>
+        <v>83208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505417</v>
+        <v>505388</v>
       </c>
       <c r="R16" t="n">
-        <v>7115033</v>
+        <v>7115116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285077</v>
+        <v>134285017</v>
       </c>
       <c r="B17" t="n">
-        <v>83208</v>
+        <v>91960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505388</v>
+        <v>505417</v>
       </c>
       <c r="R17" t="n">
-        <v>7115116</v>
+        <v>7115033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 24811-2026 artfynd.xlsx
+++ b/artfynd/A 24811-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134285061</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134285045</v>
       </c>
       <c r="B3" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>134285047</v>
       </c>
       <c r="B4" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>134285072</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>134285060</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>134285052</v>
       </c>
       <c r="B7" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285054</v>
+        <v>134285071</v>
       </c>
       <c r="B8" t="n">
-        <v>91956</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505637</v>
+        <v>505440</v>
       </c>
       <c r="R8" t="n">
-        <v>7115293</v>
+        <v>7115147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285071</v>
+        <v>134285054</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>91963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505440</v>
+        <v>505637</v>
       </c>
       <c r="R9" t="n">
-        <v>7115147</v>
+        <v>7115293</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>134285080</v>
       </c>
       <c r="B10" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>134285067</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>134285065</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>134285066</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>134285053</v>
       </c>
       <c r="B14" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>134285070</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285077</v>
+        <v>134285017</v>
       </c>
       <c r="B16" t="n">
-        <v>83208</v>
+        <v>91967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505388</v>
+        <v>505417</v>
       </c>
       <c r="R16" t="n">
-        <v>7115116</v>
+        <v>7115033</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285017</v>
+        <v>134285077</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>83215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505417</v>
+        <v>505388</v>
       </c>
       <c r="R17" t="n">
-        <v>7115033</v>
+        <v>7115116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>134285069</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>134285068</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2026 artfynd.xlsx
+++ b/artfynd/A 24811-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134285061</v>
+        <v>134285080</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505539</v>
+        <v>505394</v>
       </c>
       <c r="R2" t="n">
-        <v>7115226</v>
+        <v>7115051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134285045</v>
+        <v>134285052</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505417</v>
+        <v>505380</v>
       </c>
       <c r="R3" t="n">
-        <v>7115035</v>
+        <v>7115115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134285047</v>
+        <v>134285053</v>
       </c>
       <c r="B4" t="n">
-        <v>80481</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505537</v>
+        <v>505407</v>
       </c>
       <c r="R4" t="n">
-        <v>7115203</v>
+        <v>7115106</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134285072</v>
+        <v>134285054</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505554</v>
+        <v>505637</v>
       </c>
       <c r="R5" t="n">
-        <v>7115208</v>
+        <v>7115293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134285060</v>
+        <v>134285017</v>
       </c>
       <c r="B6" t="n">
-        <v>91981</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505319</v>
+        <v>505417</v>
       </c>
       <c r="R6" t="n">
-        <v>7114993</v>
+        <v>7115033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134285052</v>
+        <v>134285060</v>
       </c>
       <c r="B7" t="n">
-        <v>91963</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505319</v>
       </c>
       <c r="R7" t="n">
-        <v>7115115</v>
+        <v>7114993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285071</v>
+        <v>134285061</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505440</v>
+        <v>505539</v>
       </c>
       <c r="R8" t="n">
-        <v>7115147</v>
+        <v>7115226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285054</v>
+        <v>134285045</v>
       </c>
       <c r="B9" t="n">
-        <v>91963</v>
+        <v>92406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505637</v>
+        <v>505417</v>
       </c>
       <c r="R9" t="n">
-        <v>7115293</v>
+        <v>7115035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134285080</v>
+        <v>134285077</v>
       </c>
       <c r="B10" t="n">
-        <v>89347</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505394</v>
+        <v>505388</v>
       </c>
       <c r="R10" t="n">
-        <v>7115051</v>
+        <v>7115116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,14 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134285067</v>
+        <v>134285065</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505304</v>
+        <v>505546</v>
       </c>
       <c r="R11" t="n">
-        <v>7115088</v>
+        <v>7115146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,14 +1650,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134285065</v>
+        <v>134285066</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505546</v>
+        <v>505287</v>
       </c>
       <c r="R12" t="n">
-        <v>7115146</v>
+        <v>7114996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,14 +1752,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134285066</v>
+        <v>134285067</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505287</v>
+        <v>505304</v>
       </c>
       <c r="R13" t="n">
-        <v>7114996</v>
+        <v>7115088</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134285053</v>
+        <v>134285068</v>
       </c>
       <c r="B14" t="n">
-        <v>91963</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505407</v>
+        <v>505310</v>
       </c>
       <c r="R14" t="n">
-        <v>7115106</v>
+        <v>7115123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mycket riktigt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,14 +1956,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134285070</v>
+        <v>134285069</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505363</v>
+        <v>505326</v>
       </c>
       <c r="R15" t="n">
-        <v>7115111</v>
+        <v>7115123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285017</v>
+        <v>134285070</v>
       </c>
       <c r="B16" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505417</v>
+        <v>505363</v>
       </c>
       <c r="R16" t="n">
-        <v>7115033</v>
+        <v>7115111</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285077</v>
+        <v>134285071</v>
       </c>
       <c r="B17" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505388</v>
+        <v>505440</v>
       </c>
       <c r="R17" t="n">
-        <v>7115116</v>
+        <v>7115147</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,14 +2252,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134285069</v>
+        <v>134285072</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2277,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505326</v>
+        <v>505554</v>
       </c>
       <c r="R18" t="n">
-        <v>7115123</v>
+        <v>7115208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2313,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285068</v>
+        <v>134285047</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505310</v>
+        <v>505537</v>
       </c>
       <c r="R19" t="n">
-        <v>7115123</v>
+        <v>7115203</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket riktigt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 24811-2026 artfynd.xlsx
+++ b/artfynd/A 24811-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285052</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285053</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285060</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285061</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285045</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285077</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285065</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285066</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285067</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285068</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285069</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285070</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285071</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285072</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,8 +2533,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>